--- a/data/triple_music/triple_music_questions.xlsx
+++ b/data/triple_music/triple_music_questions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\Party-game\data\triple_music\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D9D6F6-DB9A-4095-95F4-BD51E32E4B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB1591EE-0DB9-4E22-BACA-3F7784A7F157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="10440" windowWidth="19380" windowHeight="10530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="38380" windowHeight="20860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tracks" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2930" uniqueCount="1804">
   <si>
     <t>ID</t>
   </si>
@@ -2456,13 +2456,4446 @@
   </si>
   <si>
     <t>t342</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt343_zhou-shen_xiao-mei-man.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t344_zhou-shen_xiao-mei-man.mp3</t>
+  </si>
+  <si>
+    <t>小美满</t>
+  </si>
+  <si>
+    <t>周深</t>
+  </si>
+  <si>
+    <t>t344</t>
+  </si>
+  <si>
+    <t>tt343</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt345_zhou-shen_qi-feng-le.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t346_zhou-shen_qi-feng-le.mp3</t>
+  </si>
+  <si>
+    <t>起风了</t>
+  </si>
+  <si>
+    <t>t346</t>
+  </si>
+  <si>
+    <t>tt345</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt347_zhou-shen_da-yu.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t348_zhou-shen_da-yu.mp3</t>
+  </si>
+  <si>
+    <t>大鱼</t>
+  </si>
+  <si>
+    <t>t348</t>
+  </si>
+  <si>
+    <t>tt347</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t349_mao-bu-yi_wu-ming-de-ren.mp3</t>
+  </si>
+  <si>
+    <t>无名的人</t>
+  </si>
+  <si>
+    <t>毛不易</t>
+  </si>
+  <si>
+    <t>t349</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt350_mao-bu-yi_xiang-wo-zhe-yang-de-ren.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t351_mao-bu-yi_xiang-wo-zhe-yang-de-ren.mp3</t>
+  </si>
+  <si>
+    <t>像我这样的人</t>
+  </si>
+  <si>
+    <t>t351</t>
+  </si>
+  <si>
+    <t>tt350</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt352_mao-bu-yi_wu-wen.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t353_mao-bu-yi_wu-wen.mp3</t>
+  </si>
+  <si>
+    <t>无问</t>
+  </si>
+  <si>
+    <t>t353</t>
+  </si>
+  <si>
+    <t>tt352</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt354_mao-bu-yi_ru-hai.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t355_mao-bu-yi_ru-hai.mp3</t>
+  </si>
+  <si>
+    <t>入海</t>
+  </si>
+  <si>
+    <t>t355</t>
+  </si>
+  <si>
+    <t>tt354</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt356_mao-bu-yi_zhi-zai-jin-ye.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t357_mao-bu-yi_zhi-zai-jin-ye.mp3</t>
+  </si>
+  <si>
+    <t>只在今夜</t>
+  </si>
+  <si>
+    <t>t357</t>
+  </si>
+  <si>
+    <t>tt356</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt358_mao-bu-yi_xiao-chou.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t359_mao-bu-yi_xiao-chou.mp3</t>
+  </si>
+  <si>
+    <t>消愁</t>
+  </si>
+  <si>
+    <t>t359</t>
+  </si>
+  <si>
+    <t>tt358</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t360_zhang-liang-ying_hua-xin.mp3</t>
+  </si>
+  <si>
+    <t>画心</t>
+  </si>
+  <si>
+    <t>张靓颖</t>
+  </si>
+  <si>
+    <t>t360</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t361_zhang-liang-ying_ye-xin-jia.mp3</t>
+  </si>
+  <si>
+    <t>野心家</t>
+  </si>
+  <si>
+    <t>t361</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt362_zhang-liang-ying_ru-guo-zhe-jiu-shi-ai-qing.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t363_zhang-liang-ying_ru-guo-zhe-jiu-shi-ai-qing.mp3</t>
+  </si>
+  <si>
+    <t>如果这就是爱情</t>
+  </si>
+  <si>
+    <t>t363</t>
+  </si>
+  <si>
+    <t>tt362</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt364_zhang-liang-ying_zhong-yu-deng-dao-ni.mp3</t>
+  </si>
+  <si>
+    <t>终于等到你</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t365_zhang-liang-ying_zhong-yu-deng-dao-ni.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t366_zhang-liang-ying_zhong-yu-deng-dao-ni.mp3</t>
+  </si>
+  <si>
+    <t>t365</t>
+  </si>
+  <si>
+    <t>t366</t>
+  </si>
+  <si>
+    <t>tt364</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t367_zhang-liang-ying_wo-men-shuo-hao-de.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t368_zhang-liang-ying_wo-men-shuo-hao-de.mp3</t>
+  </si>
+  <si>
+    <t>我们说好的</t>
+  </si>
+  <si>
+    <t>t367</t>
+  </si>
+  <si>
+    <t>t368</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t369_zhang-liang-ying_jiu-wan-zi.mp3</t>
+  </si>
+  <si>
+    <t>九万字</t>
+  </si>
+  <si>
+    <t>t369</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t370_zhang-liang-ying_ru-guo-ai-xia-qu.mp3</t>
+  </si>
+  <si>
+    <t>如果爱下去</t>
+  </si>
+  <si>
+    <t>t370</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt371_shan-yi-chun_deng-ni-shi-feng-qi.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t372_shan-yi-chun_deng-ni-shi-feng-qi.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t373_shan-yi-chun_deng-ni-shi-feng-qi.mp3</t>
+  </si>
+  <si>
+    <t>想你时风起</t>
+  </si>
+  <si>
+    <t>单依纯</t>
+  </si>
+  <si>
+    <t>t372</t>
+  </si>
+  <si>
+    <t>t373</t>
+  </si>
+  <si>
+    <t>tt371</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t374_shan-yi-chun_yong-bu-shi-lian-de-ai.mp3</t>
+  </si>
+  <si>
+    <t>永不失联的爱</t>
+  </si>
+  <si>
+    <t>t374</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t375_shan-yi-chun_li-bai.mp3</t>
+  </si>
+  <si>
+    <t>李白</t>
+  </si>
+  <si>
+    <t>t375</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt376_shan-yi-chun_chun-mei-mei.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t377_shan-yi-chun_chun-mei-mei.mp3</t>
+  </si>
+  <si>
+    <t>纯妹妹</t>
+  </si>
+  <si>
+    <t>t377</t>
+  </si>
+  <si>
+    <t>tt376</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t378_shan-yi-chun_zai-ye-li-tiao-wu.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t380_hai-lai-a-mu_ni-de-wan-shui-qian-shan.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t379_shan-yi-chun_zai-ye-li-tiao-wu.mp3</t>
+  </si>
+  <si>
+    <t>在夜里跳舞</t>
+  </si>
+  <si>
+    <t>t378</t>
+  </si>
+  <si>
+    <t>t379</t>
+  </si>
+  <si>
+    <t>t380</t>
+  </si>
+  <si>
+    <t>海来阿木</t>
+  </si>
+  <si>
+    <t>你的万水千山</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt381_beyond_hai-kuo-tian-kong.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t382_beyond_hai-kuo-tian-kong.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t383_beyond_hai-kuo-tian-kong.mp3</t>
+  </si>
+  <si>
+    <t>海阔天空</t>
+  </si>
+  <si>
+    <t>Beyond</t>
+  </si>
+  <si>
+    <t>t382</t>
+  </si>
+  <si>
+    <t>t383</t>
+  </si>
+  <si>
+    <t>tt381</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt384_beyond_guang-hui-sui-yue.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t385_beyond_guang-hui-sui-yue.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t386_beyond_guang-hui-sui-yue.mp3</t>
+  </si>
+  <si>
+    <t>光辉岁月</t>
+  </si>
+  <si>
+    <t>t385</t>
+  </si>
+  <si>
+    <t>t386</t>
+  </si>
+  <si>
+    <t>tt384</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt387_beyond_zhen-de-ai-ni.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t388_beyond_zhen-de-ai-ni.mp3</t>
+  </si>
+  <si>
+    <t>真的爱你</t>
+  </si>
+  <si>
+    <t>t388</t>
+  </si>
+  <si>
+    <t>tt387</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t389_beyond_leng-yu-ye.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t390_beyond_leng-yu-ye.mp3</t>
+  </si>
+  <si>
+    <t>冷雨夜</t>
+  </si>
+  <si>
+    <t>t389</t>
+  </si>
+  <si>
+    <t>t390</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt391_beyond_qing-ren.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t392_beyond_qing-ren.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t393_beyond_qing-ren.mp3</t>
+  </si>
+  <si>
+    <t>情人</t>
+  </si>
+  <si>
+    <t>t392</t>
+  </si>
+  <si>
+    <t>t393</t>
+  </si>
+  <si>
+    <t>tt391</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt394_beyond_amani.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t395_beyond_amani.mp3</t>
+  </si>
+  <si>
+    <t>AMANI</t>
+  </si>
+  <si>
+    <t>t395</t>
+  </si>
+  <si>
+    <t>tt394</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t396_cheng-xiang_ke-neng.mp3</t>
+  </si>
+  <si>
+    <t>可能</t>
+  </si>
+  <si>
+    <t>程响</t>
+  </si>
+  <si>
+    <t>t396</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt397_wang-fei_ru-yuan.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t398_wang-fei_ru-yuan.mp3</t>
+  </si>
+  <si>
+    <t>如愿</t>
+  </si>
+  <si>
+    <t>王菲</t>
+  </si>
+  <si>
+    <t>t398</t>
+  </si>
+  <si>
+    <t>tt397</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t399_wang-fei_shi-jie-zeng-yu-wo-de.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t400_wang-fei_shi-jie-zeng-yu-wo-de.mp3</t>
+  </si>
+  <si>
+    <t>世界赠与我的</t>
+  </si>
+  <si>
+    <t>t399</t>
+  </si>
+  <si>
+    <t>t400</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt401_wang-fei_hong-dou.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t402_wang-fei_hong-dou.mp3</t>
+  </si>
+  <si>
+    <t>红豆</t>
+  </si>
+  <si>
+    <t>t402</t>
+  </si>
+  <si>
+    <t>tt401</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt403_wang-fei_cong-cong-na-nian.mp3</t>
+  </si>
+  <si>
+    <t>匆匆那年</t>
+  </si>
+  <si>
+    <t>t404</t>
+  </si>
+  <si>
+    <t>tt403</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t405_wang-fei_chuan-qi.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t406_wang-fei_chuan-qi.mp3</t>
+  </si>
+  <si>
+    <t>传奇</t>
+  </si>
+  <si>
+    <t>t405</t>
+  </si>
+  <si>
+    <t>t406</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt407_wang-fei_wo-yuan-yi.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t408_wang-fei_wo-yuan-yi.mp3</t>
+  </si>
+  <si>
+    <t>我愿意</t>
+  </si>
+  <si>
+    <t>t408</t>
+  </si>
+  <si>
+    <t>tt407</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t409_wang-fei_bai-nian-gu-ji.mp3</t>
+  </si>
+  <si>
+    <t>百年孤寂</t>
+  </si>
+  <si>
+    <t>t409</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt410_wang-fei_liu-nian.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t411_wang-fei_liu-nian.mp3</t>
+  </si>
+  <si>
+    <t>流年</t>
+  </si>
+  <si>
+    <t>t411</t>
+  </si>
+  <si>
+    <t>tt410</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t412_wang-fei_zhi-qing-chun.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t413_wang-fei_zhi-qing-chun.mp3</t>
+  </si>
+  <si>
+    <t>致青春</t>
+  </si>
+  <si>
+    <t>t412</t>
+  </si>
+  <si>
+    <t>t413</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt414_wang-fei_gei-zi-ji-de-qing-shu.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t415_wang-fei_gei-zi-ji-de-qing-shu.mp3</t>
+  </si>
+  <si>
+    <t>给自己的情书</t>
+  </si>
+  <si>
+    <t>t415</t>
+  </si>
+  <si>
+    <t>tt414</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt416_dao-lang_chong-dong-de-cheng-fa.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t417_dao-lang_chong-dong-de-cheng-fa.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t418_dao-lang_chong-dong-de-cheng-fa.mp3</t>
+  </si>
+  <si>
+    <t>冲动的惩罚</t>
+  </si>
+  <si>
+    <t>刀郎</t>
+  </si>
+  <si>
+    <t>t417</t>
+  </si>
+  <si>
+    <t>t418</t>
+  </si>
+  <si>
+    <t>tt416</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t419_dao-lang_xi-hai-qing-ge.mp3</t>
+  </si>
+  <si>
+    <t>西海情歌</t>
+  </si>
+  <si>
+    <t>t419</t>
+  </si>
+  <si>
+    <t>2002年的第一场雪</t>
+  </si>
+  <si>
+    <t>t420</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t420_dao-lang_2002-nian-de-di-yi-chang-xue.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t421_dao-lang_pi-zhe-yang-pi-de-lang.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t422_dao-lang_pi-zhe-yang-pi-de-lang.mp3</t>
+  </si>
+  <si>
+    <t>披着羊皮的狼</t>
+  </si>
+  <si>
+    <t>t421</t>
+  </si>
+  <si>
+    <t>t422</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t423_zhang-xue-you_wen-bie.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t424_zhang-xue-you_wen-bie.mp3</t>
+  </si>
+  <si>
+    <t>吻别</t>
+  </si>
+  <si>
+    <t>t423</t>
+  </si>
+  <si>
+    <t>t424</t>
+  </si>
+  <si>
+    <t>张学友</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt425_zhang-xue-you_yi-qian-ge-shang-xin-de-li-you.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t426_zhang-xue-you_yi-qian-ge-shang-xin-de-li-you.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t427_zhang-xue-you_yi-qian-ge-shang-xin-de-li-you.mp3</t>
+  </si>
+  <si>
+    <t>一千个伤心的理由</t>
+  </si>
+  <si>
+    <t>t426</t>
+  </si>
+  <si>
+    <t>t427</t>
+  </si>
+  <si>
+    <t>tt425</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt428_zhang-xue-you_ru-guo-zhe-dou-bu-suan-ai.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t429_zhang-xue-you_ru-guo-zhe-dou-bu-suan-ai.mp3</t>
+  </si>
+  <si>
+    <t>如果这都不算爱</t>
+  </si>
+  <si>
+    <t>t429</t>
+  </si>
+  <si>
+    <t>tt428</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt430_zhang-xue-you_yao-yuan-de-ta.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t431_zhang-xue-you_yao-yuan-de-ta.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t432_zhang-xue-you_yao-yuan-de-ta.mp3</t>
+  </si>
+  <si>
+    <t>遥远的她</t>
+  </si>
+  <si>
+    <t>t431</t>
+  </si>
+  <si>
+    <t>t432</t>
+  </si>
+  <si>
+    <t>tt430</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t433_zhang-xue-you_yi-lu-shang-you-ni.mp3</t>
+  </si>
+  <si>
+    <t>一路上有你</t>
+  </si>
+  <si>
+    <t>t433</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt434_zhang-xue-you_man-man.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t435_zhang-xue-you_man-man.mp3</t>
+  </si>
+  <si>
+    <t>慢慢</t>
+  </si>
+  <si>
+    <t>t435</t>
+  </si>
+  <si>
+    <t>tt434</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt436_zhang-xue-you_xiang-si-feng-yu-zhong.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t437_zhang-xue-you_xiang-si-feng-yu-zhong.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t438_zhang-xue-you_xiang-si-feng-yu-zhong.mp3</t>
+  </si>
+  <si>
+    <t>相思风雨中</t>
+  </si>
+  <si>
+    <t>t437</t>
+  </si>
+  <si>
+    <t>t438</t>
+  </si>
+  <si>
+    <t>tt436</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt439_zhang-xue-you_fan-nao-ge.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t440_zhang-xue-you_fan-nao-ge.mp3</t>
+  </si>
+  <si>
+    <t>烦恼歌</t>
+  </si>
+  <si>
+    <t>t440</t>
+  </si>
+  <si>
+    <t>tt439</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt441_zhang-xue-you_li-xiang-lan.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t442_zhang-xue-you_li-xiang-lan.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t443_zhang-xue-you_li-xiang-lan.mp3</t>
+  </si>
+  <si>
+    <t>李香兰</t>
+  </si>
+  <si>
+    <t>t442</t>
+  </si>
+  <si>
+    <t>t443</t>
+  </si>
+  <si>
+    <t>tt441</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt444_zhang-xue-you_xin-ru-dao-ge.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t445_zhang-xue-you_xin-ru-dao-ge.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t446_zhang-xue-you_xin-ru-dao-ge.mp3</t>
+  </si>
+  <si>
+    <t>心如刀割</t>
+  </si>
+  <si>
+    <t>t445</t>
+  </si>
+  <si>
+    <t>t446</t>
+  </si>
+  <si>
+    <t>tt444</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t447_zhou-chuan-xiong_huang-hun.mp3</t>
+  </si>
+  <si>
+    <t>黄昏</t>
+  </si>
+  <si>
+    <t>周传雄</t>
+  </si>
+  <si>
+    <t>t447</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t448_zhou-chuan-xiong_ji-mo-sha-zhou-leng.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t449_zhou-chuan-xiong_ji-mo-sha-zhou-leng.mp3</t>
+  </si>
+  <si>
+    <t>寂寞沙洲冷</t>
+  </si>
+  <si>
+    <t>t448</t>
+  </si>
+  <si>
+    <t>t449</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t450_zhou-chuan-xiong_hua-xiang.mp3</t>
+  </si>
+  <si>
+    <t>花香</t>
+  </si>
+  <si>
+    <t>t450</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t451_zhou-chuan-xiong_ji-shi-ben.mp3</t>
+  </si>
+  <si>
+    <t>记事本</t>
+  </si>
+  <si>
+    <t>t451</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t452_zhou-chuan-xiong_you-mei-you-yi-shou-ge-hui-rang-ni-xiang-qi-wo.mp3</t>
+  </si>
+  <si>
+    <t>有没有一首歌会让你想起我</t>
+  </si>
+  <si>
+    <t>t452</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt453_liu-de-hua_wang-qing-shui.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t454_liu-de-hua_wang-qing-shui.mp3</t>
+  </si>
+  <si>
+    <t>忘情水</t>
+  </si>
+  <si>
+    <t>刘德华</t>
+  </si>
+  <si>
+    <t>t454</t>
+  </si>
+  <si>
+    <t>tt453</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t455_liu-de-hua_yi-qi-zou-guo-de-ri-zi.mp3</t>
+  </si>
+  <si>
+    <t>一起走过的日子</t>
+  </si>
+  <si>
+    <t>t455</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t456_liu-de-hua_bing-yu.mp3</t>
+  </si>
+  <si>
+    <t>冰雨</t>
+  </si>
+  <si>
+    <t>t456</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t457_liu-de-hua_ai-ni-yi-wan-nian.mp3</t>
+  </si>
+  <si>
+    <t>爱你一万年</t>
+  </si>
+  <si>
+    <t>t457</t>
+  </si>
+  <si>
+    <t>t458</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t459_liu-de-hua_ben-xia-hai.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt460_feng-huang-chuan-qi_he-tang-yue-se.mp3</t>
+  </si>
+  <si>
+    <t>笨小孩</t>
+  </si>
+  <si>
+    <t>荷塘月色</t>
+  </si>
+  <si>
+    <t>t459</t>
+  </si>
+  <si>
+    <t>凤凰传奇</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t461_feng-huang-chuan-qi_he-tang-yue-se.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t462_feng-huang-chuan-qi_he-tang-yue-se.mp3</t>
+  </si>
+  <si>
+    <t>t461</t>
+  </si>
+  <si>
+    <t>t462</t>
+  </si>
+  <si>
+    <t>tt460</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt463_feng-huang-chuan-qi_zui-xuan-min-zu-feng.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t464_feng-huang-chuan-qi_zui-xuan-min-zu-feng.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t465_feng-huang-chuan-qi_zui-xuan-min-zu-feng.mp3</t>
+  </si>
+  <si>
+    <t>最炫民族风</t>
+  </si>
+  <si>
+    <t>t464</t>
+  </si>
+  <si>
+    <t>t465</t>
+  </si>
+  <si>
+    <t>tt463</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt466_feng-huang-chuan-qi_yue-liang-zhi-shang.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t467_feng-huang-chuan-qi_yue-liang-zhi-shang.mp3</t>
+  </si>
+  <si>
+    <t>月亮之上</t>
+  </si>
+  <si>
+    <t>t467</t>
+  </si>
+  <si>
+    <t>tt466</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt468_feng-huang-chuan-qi_zi-you-fei-xiang.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t469_feng-huang-chuan-qi_zi-you-fei-xiang.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t470_feng-huang-chuan-qi_zi-you-fei-xiang.mp3</t>
+  </si>
+  <si>
+    <t>自由飞翔</t>
+  </si>
+  <si>
+    <t>t469</t>
+  </si>
+  <si>
+    <t>t470</t>
+  </si>
+  <si>
+    <t>tt468</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt471_feng-huang-chuan-qi_wo-cong-cao-yuan-lai.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t472_feng-huang-chuan-qi_wo-cong-cao-yuan-lai.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t473_feng-huang-chuan-qi_wo-cong-cao-yuan-lai.mp3</t>
+  </si>
+  <si>
+    <t>我从草原来</t>
+  </si>
+  <si>
+    <t>t472</t>
+  </si>
+  <si>
+    <t>t473</t>
+  </si>
+  <si>
+    <t>tt471</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t474_feng-huang-chuan-qi_quan-shi-ai.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t475_feng-huang-chuan-qi_quan-shi-ai.mp3</t>
+  </si>
+  <si>
+    <t>全是爱</t>
+  </si>
+  <si>
+    <t>t474</t>
+  </si>
+  <si>
+    <t>t475</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt476_feng-huang-chuan-qi_lang-de-you-huo.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t477_feng-huang-chuan-qi_lang-de-you-huo.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t478_feng-huang-chuan-qi_lang-de-you-huo.mp3</t>
+  </si>
+  <si>
+    <t>郎的诱惑</t>
+  </si>
+  <si>
+    <t>t477</t>
+  </si>
+  <si>
+    <t>t478</t>
+  </si>
+  <si>
+    <t>tt476</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt479_feng-huang-chuan-qi_deng-ai-de-mei-gui.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t480_feng-huang-chuan-qi_deng-ai-de-mei-gui.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t481_feng-huang-chuan-qi_deng-ai-de-mei-gui.mp3</t>
+  </si>
+  <si>
+    <t>等爱的玫瑰</t>
+  </si>
+  <si>
+    <t>t480</t>
+  </si>
+  <si>
+    <t>t481</t>
+  </si>
+  <si>
+    <t>tt479</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t482_feng-huang-chuan-qi_ce-ma-ben-teng.mp3</t>
+  </si>
+  <si>
+    <t>策马奔腾</t>
+  </si>
+  <si>
+    <t>t482</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t483_xu-song_xiang-xiang-zhi-zhong.mp3</t>
+  </si>
+  <si>
+    <t>想象之中</t>
+  </si>
+  <si>
+    <t>许嵩</t>
+  </si>
+  <si>
+    <t>t483</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t484_xu-song_quan-qiu-bian-leng.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t485_xu-song_hui-ren-bu-juan.mp3</t>
+  </si>
+  <si>
+    <t>全球变冷</t>
+  </si>
+  <si>
+    <t>毁人不倦</t>
+  </si>
+  <si>
+    <t>t484</t>
+  </si>
+  <si>
+    <t>t485</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt486_xu-song_cheng-fu.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t487_xu-song_cheng-fu.mp3</t>
+  </si>
+  <si>
+    <t>城府</t>
+  </si>
+  <si>
+    <t>t487</t>
+  </si>
+  <si>
+    <t>tt486</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt488_xu-song_qian-bai-du.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t489_xu-song_qian-bai-du.mp3</t>
+  </si>
+  <si>
+    <t>千百度</t>
+  </si>
+  <si>
+    <t>t489</t>
+  </si>
+  <si>
+    <t>tt488</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt490_xu-song_ban-cheng-yan-sha.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t491_xu-song_ban-cheng-yan-sha.mp3</t>
+  </si>
+  <si>
+    <t>半城烟沙</t>
+  </si>
+  <si>
+    <t>t491</t>
+  </si>
+  <si>
+    <t>tt490</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t492_xu-song_tian-long-ba-bu-zhi-su-di.mp3</t>
+  </si>
+  <si>
+    <t>天龙八部之宿敌</t>
+  </si>
+  <si>
+    <t>t492</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt493_xu-song_hui-se-tou-xiang.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t494_xu-song_hui-se-tou-xiang.mp3</t>
+  </si>
+  <si>
+    <t>灰色头像</t>
+  </si>
+  <si>
+    <t>t494</t>
+  </si>
+  <si>
+    <t>tt493</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t495_xu-song_lu-zhou-yue.mp3</t>
+  </si>
+  <si>
+    <t>庐州月</t>
+  </si>
+  <si>
+    <t>t495</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt496_xu-song_huan-ting.mp3</t>
+  </si>
+  <si>
+    <t>幻听</t>
+  </si>
+  <si>
+    <t>t497</t>
+  </si>
+  <si>
+    <t>tt496</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t497_xu-song_huan-ting.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t498_xu-song_qing-ming-yu-shang.mp3</t>
+  </si>
+  <si>
+    <t>清明雨上</t>
+  </si>
+  <si>
+    <t>t498</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t499_xu-song_duan-qiao-can-xue.mp3</t>
+  </si>
+  <si>
+    <t>断桥残雪</t>
+  </si>
+  <si>
+    <t>t499</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt500_xu-song_mei-gui-hua-de-zang-li.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t501_xu-song_mei-gui-hua-de-zang-li.mp3</t>
+  </si>
+  <si>
+    <t>玫瑰花的葬礼</t>
+  </si>
+  <si>
+    <t>t501</t>
+  </si>
+  <si>
+    <t>tt500</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt502_xu-song_ru-guo-dang-shi.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t503_xu-song_ru-guo-dang-shi.mp3</t>
+  </si>
+  <si>
+    <t>如果当时</t>
+  </si>
+  <si>
+    <t>t503</t>
+  </si>
+  <si>
+    <t>tt502</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt504_xu-song_su-yan.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t505_xu-song_su-yan.mp3</t>
+  </si>
+  <si>
+    <t>素颜</t>
+  </si>
+  <si>
+    <t>t505</t>
+  </si>
+  <si>
+    <t>tt504</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt506_xu-song_you-he-bu-ke.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t507_xu-song_you-he-bu-ke.mp3</t>
+  </si>
+  <si>
+    <t>有何不可</t>
+  </si>
+  <si>
+    <t>t507</t>
+  </si>
+  <si>
+    <t>tt506</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt508_wang-su-long_you-dian-tian.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t509_wang-su-long_you-dian-tian.mp3</t>
+  </si>
+  <si>
+    <t>有点甜</t>
+  </si>
+  <si>
+    <t>汪苏泷</t>
+  </si>
+  <si>
+    <t>t509</t>
+  </si>
+  <si>
+    <t>tt508</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt510_wang-su-long_bu-fen-shou-de-lian-ai.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t511_wang-su-long_bu-fen-shou-de-lian-ai.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t512_wang-su-long_bu-fen-shou-de-lian-ai.mp3</t>
+  </si>
+  <si>
+    <t>不分手的恋爱</t>
+  </si>
+  <si>
+    <t>t511</t>
+  </si>
+  <si>
+    <t>t512</t>
+  </si>
+  <si>
+    <t>tt510</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt513_wang-su-long_hou-hui-wu-qi.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t514_wang-su-long_hou-hui-wu-qi.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t515_wang-su-long_hou-hui-wu-qi.mp3</t>
+  </si>
+  <si>
+    <t>t514</t>
+  </si>
+  <si>
+    <t>t515</t>
+  </si>
+  <si>
+    <t>tt513</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt516_wang-su-long_nian-lun.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t517_wang-su-long_nian-lun.mp3</t>
+  </si>
+  <si>
+    <t>年轮</t>
+  </si>
+  <si>
+    <t>t517</t>
+  </si>
+  <si>
+    <t>tt516</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t518_wang-li-hong_da-cheng-xiao-ai.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t519_wang-li-hong_da-cheng-xiao-ai.mp3</t>
+  </si>
+  <si>
+    <t>大城小爱</t>
+  </si>
+  <si>
+    <t>王力宏</t>
+  </si>
+  <si>
+    <t>t518</t>
+  </si>
+  <si>
+    <t>t519</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt520_wang-li-hong_wo-men-de-ge.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t521_wang-li-hong_wo-men-de-ge.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t522_wang-li-hong_wo-men-de-ge.mp3</t>
+  </si>
+  <si>
+    <t>我们的歌</t>
+  </si>
+  <si>
+    <t>t521</t>
+  </si>
+  <si>
+    <t>t522</t>
+  </si>
+  <si>
+    <t>tt520</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t523_wang-li-hong_hua-tian-cuo.mp3</t>
+  </si>
+  <si>
+    <t>花田错</t>
+  </si>
+  <si>
+    <t>t523</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt524_wang-li-hong_xin-tiao.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t525_wang-li-hong_xin-tiao.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t526_wang-li-hong_xin-tiao.mp3</t>
+  </si>
+  <si>
+    <t>心跳</t>
+  </si>
+  <si>
+    <t>t525</t>
+  </si>
+  <si>
+    <t>t526</t>
+  </si>
+  <si>
+    <t>tt524</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t527_wang-li-hong_ni-bu-zhi-dao-de-shi.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t528_wang-li-hong_ni-bu-zhi-dao-de-shi.mp3</t>
+  </si>
+  <si>
+    <t>你不知道的事</t>
+  </si>
+  <si>
+    <t>t527</t>
+  </si>
+  <si>
+    <t>t528</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt529_wang-li-hong_gai-bian-zi-ji.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t530_wang-li-hong_gai-bian-zi-ji.mp3</t>
+  </si>
+  <si>
+    <t>改变自己</t>
+  </si>
+  <si>
+    <t>t530</t>
+  </si>
+  <si>
+    <t>tt529</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt531_wang-li-hong_wei-yi.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t532_wang-li-hong_wei-yi.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t533_wang-li-hong_wei-yi.mp3</t>
+  </si>
+  <si>
+    <t>唯一</t>
+  </si>
+  <si>
+    <t>t532</t>
+  </si>
+  <si>
+    <t>t533</t>
+  </si>
+  <si>
+    <t>tt531</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t534_wang-li-hong_xu-yao-ren-pei.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t535_wang-li-hong_xu-yao-ren-pei.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t536_wang-li-hong_xu-yao-ren-pei.mp3</t>
+  </si>
+  <si>
+    <t>需要人陪</t>
+  </si>
+  <si>
+    <t>t534</t>
+  </si>
+  <si>
+    <t>t535</t>
+  </si>
+  <si>
+    <t>t536</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t537_wang-li-hong_ling-yi-ge-tian-tang.mp3</t>
+  </si>
+  <si>
+    <t>另一个天堂</t>
+  </si>
+  <si>
+    <t>t537</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t538_wang-li-hong_yi-ran-ai-ni.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t539_wang-li-hong_yi-ran-ai-ni.mp3</t>
+  </si>
+  <si>
+    <t>依然爱你</t>
+  </si>
+  <si>
+    <t>t538</t>
+  </si>
+  <si>
+    <t>t539</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t540_wang-li-hong_yi-shou-jian-dan-de-ge.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t541_wang-li-hong_yi-shou-jian-dan-de-ge.mp3</t>
+  </si>
+  <si>
+    <t>一首简单的歌</t>
+  </si>
+  <si>
+    <t>t540</t>
+  </si>
+  <si>
+    <t>t541</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt542_wang-li-hong_forever-love.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t543_wang-li-hong_forever-love.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t544_wang-li-hong_forever-love.mp3</t>
+  </si>
+  <si>
+    <t>Forever Love</t>
+  </si>
+  <si>
+    <t>t543</t>
+  </si>
+  <si>
+    <t>t544</t>
+  </si>
+  <si>
+    <t>tt542</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt545_wang-li-hong_kiss-goodbye.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t546_wang-li-hong_kiss-goodbye.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t547_wang-li-hong_kiss-goodbye.mp3</t>
+  </si>
+  <si>
+    <t>Kiss Goodbye</t>
+  </si>
+  <si>
+    <t>t546</t>
+  </si>
+  <si>
+    <t>t547</t>
+  </si>
+  <si>
+    <t>tt545</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t548_wang-li-hong_ai-de-jiu-shi-ni.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt549_wang-li-hong_ai-cuo.mp3</t>
+  </si>
+  <si>
+    <t>爱的就是你</t>
+  </si>
+  <si>
+    <t>爱错</t>
+  </si>
+  <si>
+    <t>t548</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t550_wang-li-hong_ai-cuo.mp3</t>
+  </si>
+  <si>
+    <t>t550</t>
+  </si>
+  <si>
+    <t>tt549</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t551_zhang-jie_zhe-jiu-shi-ai.mp3</t>
+  </si>
+  <si>
+    <t>这就是爱</t>
+  </si>
+  <si>
+    <t>张杰</t>
+  </si>
+  <si>
+    <t>t551</t>
+  </si>
+  <si>
+    <t>只要平凡</t>
+  </si>
+  <si>
+    <t>t552</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t552_zhang-jie_zhi-yao-ping-fan.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t553_zhang-jie_san-sheng-san-shi.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t554_zhang-jie_ta-bu-dong.mp3</t>
+  </si>
+  <si>
+    <t>三生三世</t>
+  </si>
+  <si>
+    <t>他不懂</t>
+  </si>
+  <si>
+    <t>t553</t>
+  </si>
+  <si>
+    <t>t554</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt555_zhao-lei_cheng-du.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t556_zhao-lei_cheng-du.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t557_zhao-lei_cheng-du.mp3</t>
+  </si>
+  <si>
+    <t>成都</t>
+  </si>
+  <si>
+    <t>赵雷</t>
+  </si>
+  <si>
+    <t>t556</t>
+  </si>
+  <si>
+    <t>t557</t>
+  </si>
+  <si>
+    <t>tt555</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt558_zhao-lei_wo-ji-de.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t559_zhao-lei_wo-ji-de.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t560_zhao-lei_wo-ji-de.mp3</t>
+  </si>
+  <si>
+    <t>我记得</t>
+  </si>
+  <si>
+    <t>t559</t>
+  </si>
+  <si>
+    <t>t560</t>
+  </si>
+  <si>
+    <t>tt558</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt561_zhao-lei_nan-fang-gu-niang.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t562_zhao-lei_nan-fang-gu-niang.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t563_zhao-lei_nan-fang-gu-niang.mp3</t>
+  </si>
+  <si>
+    <t>南方姑娘</t>
+  </si>
+  <si>
+    <t>t562</t>
+  </si>
+  <si>
+    <t>t563</t>
+  </si>
+  <si>
+    <t>tt561</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt564_zhao-lei_hua.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t565_zhao-lei_hua.mp3</t>
+  </si>
+  <si>
+    <t>画</t>
+  </si>
+  <si>
+    <t>t565</t>
+  </si>
+  <si>
+    <t>tt564</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt566_zhao-lei_a-diao.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t567_zhao-lei_a-diao.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t568_zhao-lei_a-diao.mp3</t>
+  </si>
+  <si>
+    <t>阿刁</t>
+  </si>
+  <si>
+    <t>t567</t>
+  </si>
+  <si>
+    <t>t568</t>
+  </si>
+  <si>
+    <t>tt566</t>
+  </si>
+  <si>
+    <t>assets/triple_music/tt569_zhao-lei_shao-nian-jin-shi.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t570_zhao-lei_shao-nian-jin-shi.mp3</t>
+  </si>
+  <si>
+    <t>assets/triple_music/t571_zhao-lei_shao-nian-jin-shi.mp3</t>
+  </si>
+  <si>
+    <t>少年锦时</t>
+  </si>
+  <si>
+    <t>t570</t>
+  </si>
+  <si>
+    <t>t571</t>
+  </si>
+  <si>
+    <t>tt569</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>tt572_ren-xian-qi_shang-xin-tai-ping-yang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t573_ren-xian-qi_shang-xin-tai-ping-yang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>伤心太平洋</t>
+  </si>
+  <si>
+    <t>任贤齐</t>
+  </si>
+  <si>
+    <t>t573</t>
+  </si>
+  <si>
+    <t>tt572</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t574_ren-xian-qi_xin-tai-ruan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>心太软</t>
+  </si>
+  <si>
+    <t>t574</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t575_ren-xian-qi_lang-hua-yi-duo-duo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t576_ren-xian-qi_lang-hua-yi-duo-duo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>浪花一朵朵</t>
+  </si>
+  <si>
+    <t>t575</t>
+  </si>
+  <si>
+    <t>t576</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t577_ren-xian-qi_chun-tian-hua-hui-kai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>春天花会开</t>
+  </si>
+  <si>
+    <t>t577</t>
+  </si>
+  <si>
+    <t>t578</t>
+  </si>
+  <si>
+    <t>t579</t>
+  </si>
+  <si>
+    <t>对面的女孩看过来</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t578_ren-xian-qi_dui-mian-de-nv-hai-kan-guo-lai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t579_ren-xian-qi_dui-mian-de-nv-hai-kan-guo-lai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t580_ren-xian-qi_wo-shi-yi-zhi-yu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>我是一只鱼</t>
+  </si>
+  <si>
+    <t>t580</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t581_zhang-bi-chen_guang-de-fang-xiang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>光的方向</t>
+  </si>
+  <si>
+    <t>张碧晨</t>
+  </si>
+  <si>
+    <t>t581</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt582_zhang-bi-chen_long</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t583_zhang-bi-chen_long</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>笼</t>
+  </si>
+  <si>
+    <t>t583</t>
+  </si>
+  <si>
+    <t>tt582</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt584_zhang-bi-chen_liang-liang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t585_zhang-bi-chen_liang-liang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t586_zhang-bi-chen_liang-liang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>凉凉</t>
+  </si>
+  <si>
+    <t>t585</t>
+  </si>
+  <si>
+    <t>t586</t>
+  </si>
+  <si>
+    <t>tt584</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t587_tan-yong-lin_yi-sheng-zhong-zui-ai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>一生中最爱</t>
+  </si>
+  <si>
+    <t>谭咏麟</t>
+  </si>
+  <si>
+    <t>t587</t>
+  </si>
+  <si>
+    <t>t588</t>
+  </si>
+  <si>
+    <t>t589</t>
+  </si>
+  <si>
+    <t>朋友</t>
+  </si>
+  <si>
+    <t>讲不出再见</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t588_tan-yong-lin_peng-you</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t589_tan-yong-lin_jiang-bu-chu-zai-jian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>薛之谦</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt590_xue-zhi-qian_qi-shi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t591_xue-zhi-qian_qi-shi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>其实</t>
+  </si>
+  <si>
+    <t>t591</t>
+  </si>
+  <si>
+    <t>tt590</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt592_xue-zhi-qian_yan-yuan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t593_xue-zhi-qian_yan-yuan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>演员</t>
+  </si>
+  <si>
+    <t>t593</t>
+  </si>
+  <si>
+    <t>tt592</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt594_xue-zhi-qian_tian-wai-lai-wu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t595_xue-zhi-qian_tian-wai-lai-wu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t596_xue-zhi-qian_tian-wai-lai-wu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>天外来物</t>
+  </si>
+  <si>
+    <t>t595</t>
+  </si>
+  <si>
+    <t>t596</t>
+  </si>
+  <si>
+    <t>tt594</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt597_xue-zhi-qian_ren-zhen-de-xue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t598_xue-zhi-qian_ren-zhen-de-xue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t599_xue-zhi-qian_ren-zhen-de-xue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>认真的雪</t>
+  </si>
+  <si>
+    <t>t598</t>
+  </si>
+  <si>
+    <t>t599</t>
+  </si>
+  <si>
+    <t>tt597</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt600_xue-zhi-qian_wo-hao-xiang-zai-na-li-jian-guo-ni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>t600</t>
+  </si>
+  <si>
+    <t>t601</t>
+  </si>
+  <si>
+    <t>t602</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t601_xue-zhi-qian_wo-hao-xiang-zai-na-li-jian-guo-ni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t602_xue-zhi-qian_wo-hao-xiang-zai-na-li-jian-guo-ni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>我好像在哪见过你</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt603_xue-zhi-qian_ni-hai-yao-wo-zen-yang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t604_xue-zhi-qian_ni-hai-yao-wo-zen-yang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t605_xue-zhi-qian_ni-hai-yao-wo-zen-yang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>你还要我怎样</t>
+  </si>
+  <si>
+    <t>t604</t>
+  </si>
+  <si>
+    <t>t605</t>
+  </si>
+  <si>
+    <t>tt603</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt606_xue-zhi-qian_chou-ba-guai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t607_xue-zhi-qian_chou-ba-guai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t608_xue-zhi-qian_chou-ba-guai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>t607</t>
+  </si>
+  <si>
+    <t>t608</t>
+  </si>
+  <si>
+    <t>tt606</t>
+  </si>
+  <si>
+    <t>丑八怪</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt609_xue-zhi-qian_xiang-feng-yi-yang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t610_xue-zhi-qian_xiang-feng-yi-yang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t611_xue-zhi-qian_xiang-feng-yi-yang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>像风一样</t>
+  </si>
+  <si>
+    <t>t610</t>
+  </si>
+  <si>
+    <t>t611</t>
+  </si>
+  <si>
+    <t>tt609</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt612_xue-zhi-qian_gang-gang-hao</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t613_xue-zhi-qian_gang-gang-hao</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>刚刚好</t>
+  </si>
+  <si>
+    <t>t613</t>
+  </si>
+  <si>
+    <t>tt612</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt614_xue-zhi-qian_yi-wai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t615_xue-zhi-qian_yi-wai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>意外</t>
+  </si>
+  <si>
+    <t>t615</t>
+  </si>
+  <si>
+    <t>tt614</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t616_xue-zhi-qian_guai-ka</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>怪咖</t>
+  </si>
+  <si>
+    <t>t616</t>
+  </si>
+  <si>
+    <t>t617</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t617_xue-zhi-qian_guai-ka</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt618_xue-zhi-qian_shen-shi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t619_xue-zhi-qian_shen-shi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t620_xue-zhi-qian_shen-shi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>绅士</t>
+  </si>
+  <si>
+    <t>t619</t>
+  </si>
+  <si>
+    <t>t620</t>
+  </si>
+  <si>
+    <t>tt618</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt621_xue-zhi-qian_ai-mei</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t622_xue-zhi-qian_ai-mei</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>暧昧</t>
+  </si>
+  <si>
+    <t>t622</t>
+  </si>
+  <si>
+    <t>tt621</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t623_zhang-shao-han_mu-se-hui-xiang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>暮色回响</t>
+  </si>
+  <si>
+    <t>张韶涵</t>
+  </si>
+  <si>
+    <t>t623</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt624_zhang-shao-han_yin-xing-de-chi-bang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t625_zhang-shao-han_yin-xing-de-chi-bang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t626_zhang-shao-han_yin-xing-de-chi-bang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>隐形的翅膀</t>
+  </si>
+  <si>
+    <t>t625</t>
+  </si>
+  <si>
+    <t>t626</t>
+  </si>
+  <si>
+    <t>tt624</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t627_zhang-shao-han_lin-yu-yi-zhi-zou</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t628_zhang-shao-han_lin-yu-yi-zhi-zou</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>淋雨一直走</t>
+  </si>
+  <si>
+    <t>t627</t>
+  </si>
+  <si>
+    <t>t628</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t629_zhang-shao-han_po-jian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>破茧</t>
+  </si>
+  <si>
+    <t>t629</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt630_zhang-shao-han_kuai-le-chong-bai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t631_zhang-shao-han_kuai-le-chong-bai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>快乐崇拜</t>
+  </si>
+  <si>
+    <t>t631</t>
+  </si>
+  <si>
+    <t>tt630</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t632_zhang-shao-han_pian-zhang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>篇章</t>
+  </si>
+  <si>
+    <t>t632</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt633_zhang-shao-han_ou-ruo-la</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t634_zhang-shao-han_ou-ruo-la</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t635_zhang-shao-han_ou-ruo-la</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>欧若拉</t>
+  </si>
+  <si>
+    <t>t634</t>
+  </si>
+  <si>
+    <t>t635</t>
+  </si>
+  <si>
+    <t>tt633</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt636_zhang-shao-han_ruo-guo-de-shi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t637_zhang-shao-han_ruo-guo-de-shi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t638_zhang-shao-han_ruo-guo-de-shi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>如果的事</t>
+  </si>
+  <si>
+    <t>t637</t>
+  </si>
+  <si>
+    <t>t638</t>
+  </si>
+  <si>
+    <t>tt636</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t639_zhang-shao-han_you-xing-de-chi-bang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>有形的翅膀</t>
+  </si>
+  <si>
+    <t>t639</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt640_zhang-shao-han_qin-ai-de-na-bu-shi-ai-qing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t641_zhang-shao-han_qin-ai-de-na-bu-shi-ai-qing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t642_zhang-shao-han_qin-ai-de-na-bu-shi-ai-qing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>亲爱的，那不是爱情</t>
+  </si>
+  <si>
+    <t>t641</t>
+  </si>
+  <si>
+    <t>t642</t>
+  </si>
+  <si>
+    <t>tt640</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt643_zhang-shao-han_yi-shi-de-mei-hao</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t644_zhang-shao-han_yi-shi-de-mei-hao</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t645_zhang-shao-han_yi-shi-de-mei-hao</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>遗失的美好</t>
+  </si>
+  <si>
+    <t>t644</t>
+  </si>
+  <si>
+    <t>t645</t>
+  </si>
+  <si>
+    <t>tt643</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t646_zhang-shao-han_xiang-shui-bai-he</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt647_zhang-shao-han_meng-li-hua</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>香水百合</t>
+  </si>
+  <si>
+    <t>t646</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t648_zhang-shao-han_meng-li-hua</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t649_zhang-shao-han_meng-li-hua</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>梦里花</t>
+  </si>
+  <si>
+    <t>t648</t>
+  </si>
+  <si>
+    <t>t649</t>
+  </si>
+  <si>
+    <t>tt647</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt650_sui-yan-zi_wo-huai-nian-de</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t651_sui-yan-zi_wo-huai-nian-de</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t652_sui-yan-zi_wo-huai-nian-de</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>我怀念的</t>
+  </si>
+  <si>
+    <t>孙燕姿</t>
+  </si>
+  <si>
+    <t>t651</t>
+  </si>
+  <si>
+    <t>t652</t>
+  </si>
+  <si>
+    <t>tt650</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt653_sui-yan-zi_yu-jian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t654_sui-yan-zi_yu-jian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t655_sui-yan-zi_yu-jian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>遇见</t>
+  </si>
+  <si>
+    <t>t654</t>
+  </si>
+  <si>
+    <t>t655</t>
+  </si>
+  <si>
+    <t>tt653</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt656_sui-yan-zi_kai-shi-dong-le</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t657_sui-yan-zi_kai-shi-dong-le</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>开始懂了</t>
+  </si>
+  <si>
+    <t>t657</t>
+  </si>
+  <si>
+    <t>tt656</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t658_sui-yan-zi_lv-guang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t659_sui-yan-zi_lv-guang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>绿光</t>
+  </si>
+  <si>
+    <t>t658</t>
+  </si>
+  <si>
+    <t>t659</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t660_sui-yan-zi_tian-hei-hei</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t661_sui-yan-zi_tian-hei-hei</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>天黑黑</t>
+  </si>
+  <si>
+    <t>t660</t>
+  </si>
+  <si>
+    <t>t661</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt662_sui-yan-zi_yu-tian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t663_sui-yan-zi_yu-tian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t664_sui-yan-zi_yu-tian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>雨天</t>
+  </si>
+  <si>
+    <t>t663</t>
+  </si>
+  <si>
+    <t>t664</t>
+  </si>
+  <si>
+    <t>tt662</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt665_sui-yan-zi_ni-guang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t666_sui-yan-zi_ni-guang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t667_sui-yan-zi_ni-guang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>逆光</t>
+  </si>
+  <si>
+    <t>t666</t>
+  </si>
+  <si>
+    <t>t667</t>
+  </si>
+  <si>
+    <t>tt665</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt668_sui-yan-zi_ban-ju-zai-jian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t669_sui-yan-zi_ban-ju-zai-jian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t670_sui-yan-zi_ban-ju-zai-jian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>半句再见</t>
+  </si>
+  <si>
+    <t>t669</t>
+  </si>
+  <si>
+    <t>t670</t>
+  </si>
+  <si>
+    <t>tt668</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt671_sui-yan-zi_wo-bu-nan-guo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t672_sui-yan-zi_wo-bu-nan-guo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t673_sui-yan-zi_wo-bu-nan-guo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>我不难过</t>
+  </si>
+  <si>
+    <t>t672</t>
+  </si>
+  <si>
+    <t>t673</t>
+  </si>
+  <si>
+    <t>tt671</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt674_sui-yan-zi_wo-ye-hen-xiang-ta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t675_sui-yan-zi_wo-ye-hen-xiang-ta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t676_sui-yan-zi_wo-ye-hen-xiang-ta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>我也很想他</t>
+  </si>
+  <si>
+    <t>t675</t>
+  </si>
+  <si>
+    <t>t676</t>
+  </si>
+  <si>
+    <t>tt674</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt677_sui-yan-zi_dang-dong-ye-jian-nuan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t678_sui-yan-zi_dang-dong-ye-jian-nuan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t679_sui-yan-zi_dang-dong-ye-jian-nuan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>当冬夜渐暖</t>
+  </si>
+  <si>
+    <t>t678</t>
+  </si>
+  <si>
+    <t>t679</t>
+  </si>
+  <si>
+    <t>tt677</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt680_sui-yan-zi_yuan-lai-ni-shen-me-dou-bu-xiang-yao</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t681_sui-yan-zi_yuan-lai-ni-shen-me-dou-bu-xiang-yao</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t682_sui-yan-zi_yuan-lai-ni-shen-me-dou-bu-xiang-yao</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>原来你什么都不想要</t>
+  </si>
+  <si>
+    <t>t681</t>
+  </si>
+  <si>
+    <t>t682</t>
+  </si>
+  <si>
+    <t>tt680</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt683_sui-yan-zi_yin-xing-ren</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t684_sui-yan-zi_yin-xing-ren</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t685_sui-yan-zi_yin-xing-ren</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>隐形人</t>
+  </si>
+  <si>
+    <t>t684</t>
+  </si>
+  <si>
+    <t>t685</t>
+  </si>
+  <si>
+    <t>tt683</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t686_xu-wei_lan-lian-hua</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t687_xu-wei_lan-lian-hua</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>蓝莲花</t>
+  </si>
+  <si>
+    <t>许巍</t>
+  </si>
+  <si>
+    <t>t686</t>
+  </si>
+  <si>
+    <t>t687</t>
+  </si>
+  <si>
+    <t>曾经的你</t>
+  </si>
+  <si>
+    <t>t688</t>
+  </si>
+  <si>
+    <t>t689</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t688_xu-wei_lan-ceng-jing-de-ni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t689_xu-wei_lan-ceng-jing-de-ni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t691_xu-wei_lan-zeng-jing-de-ni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt690_xu-wei_lan-zeng-jing-de-ni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t692_xu-wei_lan-zeng-jing-de-ni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>故乡</t>
+  </si>
+  <si>
+    <t>t691</t>
+  </si>
+  <si>
+    <t>t692</t>
+  </si>
+  <si>
+    <t>tt690</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt693_xu-wei_lan-lv-xing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t694_xu-wei_lan-lv-xing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>旅行</t>
+  </si>
+  <si>
+    <t>t694</t>
+  </si>
+  <si>
+    <t>tt693</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t695_zhang-xin-zhe_guo-huo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t696_zhang-xin-zhe_guo-huo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>过火</t>
+  </si>
+  <si>
+    <t>张信哲</t>
+  </si>
+  <si>
+    <t>t695</t>
+  </si>
+  <si>
+    <t>t696</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t697_zhang-xin-zhe_ai-ru-chao-shui</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>爱如潮水</t>
+  </si>
+  <si>
+    <t>t697</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt698_zhang-xin-zhe_xin-yang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t699_zhang-xin-zhe_xin-yang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t700_zhang-xin-zhe_xin-yang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>信仰</t>
+  </si>
+  <si>
+    <t>t699</t>
+  </si>
+  <si>
+    <t>t700</t>
+  </si>
+  <si>
+    <t>tt698</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t701_zhang-xin-zhe_ai-jiu-yi-ge-zi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>爱就一个字</t>
+  </si>
+  <si>
+    <t>t701</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt702_cai-jian-ya_hong-se-gao-gen-xie</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t703_cai-jian-ya_hong-se-gao-gen-xie</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t704_cai-jian-ya_hong-se-gao-gen-xie</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>红色高跟鞋</t>
+  </si>
+  <si>
+    <t>蔡健雅</t>
+  </si>
+  <si>
+    <t>t703</t>
+  </si>
+  <si>
+    <t>t704</t>
+  </si>
+  <si>
+    <t>tt702</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt705_cai-jian-ya_yue-lai-yue-bu-dong</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t706_cai-jian-ya_yue-lai-yue-bu-dong</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t707_cai-jian-ya_yue-lai-yue-bu-dong</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>越来越不懂</t>
+  </si>
+  <si>
+    <t>t706</t>
+  </si>
+  <si>
+    <t>t707</t>
+  </si>
+  <si>
+    <t>tt705</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt708_cai-jian-ya_letting-go</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>Letting go</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t709_cai-jian-ya_letting-go</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t710_cai-jian-ya_letting-go</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>t709</t>
+  </si>
+  <si>
+    <t>t710</t>
+  </si>
+  <si>
+    <t>tt708</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t711_cai-jian-ya_zhui-luo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t712_cai-jian-ya_zhui-luo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>坠落</t>
+  </si>
+  <si>
+    <t>t711</t>
+  </si>
+  <si>
+    <t>t712</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt713_cai-jian-ya_si-nian-shi-yi-zhong-bing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t714_cai-jian-ya_si-nian-shi-yi-zhong-bing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t715_cai-jian-ya_si-nian-shi-yi-zhong-bing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>思念是一种病</t>
+  </si>
+  <si>
+    <t>t714</t>
+  </si>
+  <si>
+    <t>t715</t>
+  </si>
+  <si>
+    <t>tt713</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt716_cai-jian-ya_da-er-wen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t717_cai-jian-ya_da-er-wen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t718_cai-jian-ya_da-er-wen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>达尔文</t>
+  </si>
+  <si>
+    <t>t717</t>
+  </si>
+  <si>
+    <t>t718</t>
+  </si>
+  <si>
+    <t>tt716</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt719_cai-jian-ya_kong-bai-ge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t720_cai-jian-ya_kong-bai-ge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t721_cai-jian-ya_kong-bai-ge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>空白格</t>
+  </si>
+  <si>
+    <t>t720</t>
+  </si>
+  <si>
+    <t>t721</t>
+  </si>
+  <si>
+    <t>tt719</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt722_cai-jian-ya_shi-yu-zhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t723_cai-jian-ya_shi-yu-zhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>失语者</t>
+  </si>
+  <si>
+    <t>t722</t>
+  </si>
+  <si>
+    <t>t723</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt724_cai-jian-ya_bei-xun-fu-de-xiang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t725_cai-jian-ya_bei-xun-fu-de-xiang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t726_cai-jian-ya_bei-xun-fu-de-xiang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t727_cai-jian-ya_bei-xun-fu-de-xiang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>被驯服的象</t>
+  </si>
+  <si>
+    <t>t725</t>
+  </si>
+  <si>
+    <t>t726</t>
+  </si>
+  <si>
+    <t>t727</t>
+  </si>
+  <si>
+    <t>tt724</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/tt728_cai-jian-ya_bie-zhao-wo-ma-fan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t729_cai-jian-ya_bie-zhao-wo-ma-fan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>别找我麻烦</t>
+  </si>
+  <si>
+    <t>t729</t>
+  </si>
+  <si>
+    <t>tt728</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t730_cai-jian-ya_bai-tian-bu-dong-ye-de-hei</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>白天不懂夜的黑</t>
+  </si>
+  <si>
+    <t>t730</t>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t731_cai-jian-ya_shi-wan-hao-sheng-lei-shui</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assets/triple_music/t732_cai-jian-ya_shi-wan-hao-sheng-lei-shui</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+  </si>
+  <si>
+    <t>十万毫升泪水</t>
+  </si>
+  <si>
+    <t>t731</t>
+  </si>
+  <si>
+    <t>t732</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
@@ -2475,6 +6908,11 @@
     <font>
       <sz val="8"/>
       <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2497,12 +6935,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2837,12 +7276,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D343"/>
+  <dimension ref="A1:D733"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="65.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="21.3828125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="83.61328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -7647,6 +12087,5466 @@
         <v>808</v>
       </c>
     </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A344" t="s">
+        <v>817</v>
+      </c>
+      <c r="B344" t="s">
+        <v>815</v>
+      </c>
+      <c r="C344" t="s">
+        <v>814</v>
+      </c>
+      <c r="D344" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A345" t="s">
+        <v>816</v>
+      </c>
+      <c r="B345" t="s">
+        <v>815</v>
+      </c>
+      <c r="C345" t="s">
+        <v>814</v>
+      </c>
+      <c r="D345" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A346" t="s">
+        <v>822</v>
+      </c>
+      <c r="B346" t="s">
+        <v>815</v>
+      </c>
+      <c r="C346" t="s">
+        <v>820</v>
+      </c>
+      <c r="D346" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A347" t="s">
+        <v>821</v>
+      </c>
+      <c r="B347" t="s">
+        <v>815</v>
+      </c>
+      <c r="C347" t="s">
+        <v>820</v>
+      </c>
+      <c r="D347" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A348" t="s">
+        <v>827</v>
+      </c>
+      <c r="B348" t="s">
+        <v>815</v>
+      </c>
+      <c r="C348" t="s">
+        <v>825</v>
+      </c>
+      <c r="D348" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A349" t="s">
+        <v>826</v>
+      </c>
+      <c r="B349" t="s">
+        <v>815</v>
+      </c>
+      <c r="C349" t="s">
+        <v>825</v>
+      </c>
+      <c r="D349" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A350" t="s">
+        <v>831</v>
+      </c>
+      <c r="B350" t="s">
+        <v>830</v>
+      </c>
+      <c r="C350" t="s">
+        <v>829</v>
+      </c>
+      <c r="D350" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A351" t="s">
+        <v>836</v>
+      </c>
+      <c r="B351" t="s">
+        <v>830</v>
+      </c>
+      <c r="C351" t="s">
+        <v>834</v>
+      </c>
+      <c r="D351" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A352" t="s">
+        <v>835</v>
+      </c>
+      <c r="B352" t="s">
+        <v>830</v>
+      </c>
+      <c r="C352" t="s">
+        <v>834</v>
+      </c>
+      <c r="D352" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A353" t="s">
+        <v>841</v>
+      </c>
+      <c r="B353" t="s">
+        <v>830</v>
+      </c>
+      <c r="C353" t="s">
+        <v>839</v>
+      </c>
+      <c r="D353" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A354" t="s">
+        <v>840</v>
+      </c>
+      <c r="B354" t="s">
+        <v>830</v>
+      </c>
+      <c r="C354" t="s">
+        <v>839</v>
+      </c>
+      <c r="D354" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A355" t="s">
+        <v>846</v>
+      </c>
+      <c r="B355" t="s">
+        <v>830</v>
+      </c>
+      <c r="C355" t="s">
+        <v>844</v>
+      </c>
+      <c r="D355" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A356" t="s">
+        <v>845</v>
+      </c>
+      <c r="B356" t="s">
+        <v>830</v>
+      </c>
+      <c r="C356" t="s">
+        <v>844</v>
+      </c>
+      <c r="D356" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A357" t="s">
+        <v>851</v>
+      </c>
+      <c r="B357" t="s">
+        <v>830</v>
+      </c>
+      <c r="C357" t="s">
+        <v>849</v>
+      </c>
+      <c r="D357" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A358" t="s">
+        <v>850</v>
+      </c>
+      <c r="B358" t="s">
+        <v>830</v>
+      </c>
+      <c r="C358" t="s">
+        <v>849</v>
+      </c>
+      <c r="D358" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A359" t="s">
+        <v>856</v>
+      </c>
+      <c r="B359" t="s">
+        <v>830</v>
+      </c>
+      <c r="C359" t="s">
+        <v>854</v>
+      </c>
+      <c r="D359" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A360" t="s">
+        <v>855</v>
+      </c>
+      <c r="B360" t="s">
+        <v>830</v>
+      </c>
+      <c r="C360" t="s">
+        <v>854</v>
+      </c>
+      <c r="D360" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A361" t="s">
+        <v>860</v>
+      </c>
+      <c r="B361" t="s">
+        <v>859</v>
+      </c>
+      <c r="C361" t="s">
+        <v>858</v>
+      </c>
+      <c r="D361" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A362" t="s">
+        <v>863</v>
+      </c>
+      <c r="B362" t="s">
+        <v>859</v>
+      </c>
+      <c r="C362" t="s">
+        <v>862</v>
+      </c>
+      <c r="D362" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A363" t="s">
+        <v>868</v>
+      </c>
+      <c r="B363" t="s">
+        <v>859</v>
+      </c>
+      <c r="C363" t="s">
+        <v>866</v>
+      </c>
+      <c r="D363" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A364" t="s">
+        <v>867</v>
+      </c>
+      <c r="B364" t="s">
+        <v>859</v>
+      </c>
+      <c r="C364" t="s">
+        <v>866</v>
+      </c>
+      <c r="D364" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A365" t="s">
+        <v>875</v>
+      </c>
+      <c r="B365" t="s">
+        <v>859</v>
+      </c>
+      <c r="C365" t="s">
+        <v>870</v>
+      </c>
+      <c r="D365" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A366" t="s">
+        <v>873</v>
+      </c>
+      <c r="B366" t="s">
+        <v>859</v>
+      </c>
+      <c r="C366" t="s">
+        <v>870</v>
+      </c>
+      <c r="D366" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A367" t="s">
+        <v>874</v>
+      </c>
+      <c r="B367" t="s">
+        <v>859</v>
+      </c>
+      <c r="C367" t="s">
+        <v>870</v>
+      </c>
+      <c r="D367" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A368" t="s">
+        <v>879</v>
+      </c>
+      <c r="B368" t="s">
+        <v>859</v>
+      </c>
+      <c r="C368" t="s">
+        <v>878</v>
+      </c>
+      <c r="D368" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A369" t="s">
+        <v>880</v>
+      </c>
+      <c r="B369" t="s">
+        <v>859</v>
+      </c>
+      <c r="C369" t="s">
+        <v>878</v>
+      </c>
+      <c r="D369" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A370" t="s">
+        <v>883</v>
+      </c>
+      <c r="B370" t="s">
+        <v>859</v>
+      </c>
+      <c r="C370" t="s">
+        <v>882</v>
+      </c>
+      <c r="D370" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A371" t="s">
+        <v>886</v>
+      </c>
+      <c r="B371" t="s">
+        <v>859</v>
+      </c>
+      <c r="C371" t="s">
+        <v>885</v>
+      </c>
+      <c r="D371" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A372" t="s">
+        <v>894</v>
+      </c>
+      <c r="B372" t="s">
+        <v>891</v>
+      </c>
+      <c r="C372" t="s">
+        <v>890</v>
+      </c>
+      <c r="D372" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A373" t="s">
+        <v>892</v>
+      </c>
+      <c r="B373" t="s">
+        <v>891</v>
+      </c>
+      <c r="C373" t="s">
+        <v>890</v>
+      </c>
+      <c r="D373" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A374" t="s">
+        <v>893</v>
+      </c>
+      <c r="B374" t="s">
+        <v>891</v>
+      </c>
+      <c r="C374" t="s">
+        <v>890</v>
+      </c>
+      <c r="D374" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A375" t="s">
+        <v>897</v>
+      </c>
+      <c r="B375" t="s">
+        <v>891</v>
+      </c>
+      <c r="C375" t="s">
+        <v>896</v>
+      </c>
+      <c r="D375" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A376" t="s">
+        <v>900</v>
+      </c>
+      <c r="B376" t="s">
+        <v>891</v>
+      </c>
+      <c r="C376" t="s">
+        <v>899</v>
+      </c>
+      <c r="D376" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A377" t="s">
+        <v>905</v>
+      </c>
+      <c r="B377" t="s">
+        <v>891</v>
+      </c>
+      <c r="C377" t="s">
+        <v>903</v>
+      </c>
+      <c r="D377" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A378" t="s">
+        <v>904</v>
+      </c>
+      <c r="B378" t="s">
+        <v>891</v>
+      </c>
+      <c r="C378" t="s">
+        <v>903</v>
+      </c>
+      <c r="D378" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A379" t="s">
+        <v>910</v>
+      </c>
+      <c r="B379" t="s">
+        <v>891</v>
+      </c>
+      <c r="C379" t="s">
+        <v>909</v>
+      </c>
+      <c r="D379" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A380" t="s">
+        <v>911</v>
+      </c>
+      <c r="B380" t="s">
+        <v>891</v>
+      </c>
+      <c r="C380" t="s">
+        <v>909</v>
+      </c>
+      <c r="D380" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A381" t="s">
+        <v>912</v>
+      </c>
+      <c r="B381" t="s">
+        <v>913</v>
+      </c>
+      <c r="C381" t="s">
+        <v>914</v>
+      </c>
+      <c r="D381" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A382" t="s">
+        <v>922</v>
+      </c>
+      <c r="B382" t="s">
+        <v>919</v>
+      </c>
+      <c r="C382" t="s">
+        <v>918</v>
+      </c>
+      <c r="D382" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A383" t="s">
+        <v>920</v>
+      </c>
+      <c r="B383" t="s">
+        <v>919</v>
+      </c>
+      <c r="C383" t="s">
+        <v>918</v>
+      </c>
+      <c r="D383" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A384" t="s">
+        <v>921</v>
+      </c>
+      <c r="B384" t="s">
+        <v>919</v>
+      </c>
+      <c r="C384" t="s">
+        <v>918</v>
+      </c>
+      <c r="D384" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A385" t="s">
+        <v>929</v>
+      </c>
+      <c r="B385" t="s">
+        <v>919</v>
+      </c>
+      <c r="C385" t="s">
+        <v>926</v>
+      </c>
+      <c r="D385" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A386" t="s">
+        <v>927</v>
+      </c>
+      <c r="B386" t="s">
+        <v>919</v>
+      </c>
+      <c r="C386" t="s">
+        <v>926</v>
+      </c>
+      <c r="D386" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A387" t="s">
+        <v>928</v>
+      </c>
+      <c r="B387" t="s">
+        <v>919</v>
+      </c>
+      <c r="C387" t="s">
+        <v>926</v>
+      </c>
+      <c r="D387" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A388" t="s">
+        <v>934</v>
+      </c>
+      <c r="B388" t="s">
+        <v>919</v>
+      </c>
+      <c r="C388" t="s">
+        <v>932</v>
+      </c>
+      <c r="D388" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A389" t="s">
+        <v>933</v>
+      </c>
+      <c r="B389" t="s">
+        <v>919</v>
+      </c>
+      <c r="C389" t="s">
+        <v>932</v>
+      </c>
+      <c r="D389" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A390" t="s">
+        <v>938</v>
+      </c>
+      <c r="B390" t="s">
+        <v>919</v>
+      </c>
+      <c r="C390" t="s">
+        <v>937</v>
+      </c>
+      <c r="D390" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A391" t="s">
+        <v>939</v>
+      </c>
+      <c r="B391" t="s">
+        <v>919</v>
+      </c>
+      <c r="C391" t="s">
+        <v>937</v>
+      </c>
+      <c r="D391" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A392" t="s">
+        <v>946</v>
+      </c>
+      <c r="B392" t="s">
+        <v>919</v>
+      </c>
+      <c r="C392" t="s">
+        <v>943</v>
+      </c>
+      <c r="D392" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A393" t="s">
+        <v>944</v>
+      </c>
+      <c r="B393" t="s">
+        <v>919</v>
+      </c>
+      <c r="C393" t="s">
+        <v>943</v>
+      </c>
+      <c r="D393" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A394" t="s">
+        <v>945</v>
+      </c>
+      <c r="B394" t="s">
+        <v>919</v>
+      </c>
+      <c r="C394" t="s">
+        <v>943</v>
+      </c>
+      <c r="D394" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A395" t="s">
+        <v>951</v>
+      </c>
+      <c r="B395" t="s">
+        <v>919</v>
+      </c>
+      <c r="C395" t="s">
+        <v>949</v>
+      </c>
+      <c r="D395" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A396" t="s">
+        <v>950</v>
+      </c>
+      <c r="B396" t="s">
+        <v>919</v>
+      </c>
+      <c r="C396" t="s">
+        <v>949</v>
+      </c>
+      <c r="D396" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A397" t="s">
+        <v>955</v>
+      </c>
+      <c r="B397" t="s">
+        <v>954</v>
+      </c>
+      <c r="C397" t="s">
+        <v>953</v>
+      </c>
+      <c r="D397" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A398" t="s">
+        <v>961</v>
+      </c>
+      <c r="B398" t="s">
+        <v>959</v>
+      </c>
+      <c r="C398" t="s">
+        <v>958</v>
+      </c>
+      <c r="D398" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A399" t="s">
+        <v>960</v>
+      </c>
+      <c r="B399" t="s">
+        <v>959</v>
+      </c>
+      <c r="C399" t="s">
+        <v>958</v>
+      </c>
+      <c r="D399" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A400" t="s">
+        <v>965</v>
+      </c>
+      <c r="B400" t="s">
+        <v>959</v>
+      </c>
+      <c r="C400" t="s">
+        <v>964</v>
+      </c>
+      <c r="D400" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A401" t="s">
+        <v>966</v>
+      </c>
+      <c r="B401" t="s">
+        <v>959</v>
+      </c>
+      <c r="C401" t="s">
+        <v>964</v>
+      </c>
+      <c r="D401" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A402" t="s">
+        <v>971</v>
+      </c>
+      <c r="B402" t="s">
+        <v>959</v>
+      </c>
+      <c r="C402" t="s">
+        <v>969</v>
+      </c>
+      <c r="D402" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A403" t="s">
+        <v>970</v>
+      </c>
+      <c r="B403" t="s">
+        <v>959</v>
+      </c>
+      <c r="C403" t="s">
+        <v>969</v>
+      </c>
+      <c r="D403" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A404" t="s">
+        <v>975</v>
+      </c>
+      <c r="B404" t="s">
+        <v>959</v>
+      </c>
+      <c r="C404" t="s">
+        <v>973</v>
+      </c>
+      <c r="D404" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A405" t="s">
+        <v>974</v>
+      </c>
+      <c r="B405" t="s">
+        <v>959</v>
+      </c>
+      <c r="C405" t="s">
+        <v>973</v>
+      </c>
+      <c r="D405" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A406" t="s">
+        <v>979</v>
+      </c>
+      <c r="B406" t="s">
+        <v>959</v>
+      </c>
+      <c r="C406" t="s">
+        <v>978</v>
+      </c>
+      <c r="D406" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A407" t="s">
+        <v>980</v>
+      </c>
+      <c r="B407" t="s">
+        <v>959</v>
+      </c>
+      <c r="C407" t="s">
+        <v>978</v>
+      </c>
+      <c r="D407" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A408" t="s">
+        <v>985</v>
+      </c>
+      <c r="B408" t="s">
+        <v>959</v>
+      </c>
+      <c r="C408" t="s">
+        <v>983</v>
+      </c>
+      <c r="D408" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A409" t="s">
+        <v>984</v>
+      </c>
+      <c r="B409" t="s">
+        <v>959</v>
+      </c>
+      <c r="C409" t="s">
+        <v>983</v>
+      </c>
+      <c r="D409" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A410" t="s">
+        <v>988</v>
+      </c>
+      <c r="B410" t="s">
+        <v>959</v>
+      </c>
+      <c r="C410" t="s">
+        <v>987</v>
+      </c>
+      <c r="D410" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A411" t="s">
+        <v>993</v>
+      </c>
+      <c r="B411" t="s">
+        <v>959</v>
+      </c>
+      <c r="C411" t="s">
+        <v>991</v>
+      </c>
+      <c r="D411" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A412" t="s">
+        <v>992</v>
+      </c>
+      <c r="B412" t="s">
+        <v>959</v>
+      </c>
+      <c r="C412" t="s">
+        <v>991</v>
+      </c>
+      <c r="D412" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A413" t="s">
+        <v>997</v>
+      </c>
+      <c r="B413" t="s">
+        <v>959</v>
+      </c>
+      <c r="C413" t="s">
+        <v>996</v>
+      </c>
+      <c r="D413" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A414" t="s">
+        <v>998</v>
+      </c>
+      <c r="B414" t="s">
+        <v>959</v>
+      </c>
+      <c r="C414" t="s">
+        <v>996</v>
+      </c>
+      <c r="D414" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A415" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B415" t="s">
+        <v>959</v>
+      </c>
+      <c r="C415" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D415" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A416" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B416" t="s">
+        <v>959</v>
+      </c>
+      <c r="C416" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D416" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A417" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B417" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C417" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D417" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A418" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B418" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C418" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D418" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A419" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B419" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C419" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D419" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A420" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B420" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C420" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D420" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A421" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B421" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C421" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D421" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A422" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C422" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D422" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A423" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B423" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C423" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D423" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A424" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B424" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C424" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D424" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A425" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B425" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C425" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D425" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A426" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B426" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C426" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D426" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A427" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B427" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C427" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D427" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A428" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B428" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C428" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D428" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A429" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C429" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D429" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A430" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C430" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D430" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A431" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B431" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C431" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D431" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A432" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B432" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C432" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D432" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A433" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B433" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C433" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D433" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A434" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B434" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C434" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D434" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A435" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B435" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C435" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D435" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A436" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B436" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C436" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D436" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A437" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B437" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C437" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D437" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A438" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C438" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D438" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A439" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B439" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C439" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D439" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A440" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B440" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C440" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D440" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A441" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B441" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C441" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D441" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A442" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B442" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C442" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D442" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A443" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B443" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C443" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D443" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A444" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B444" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C444" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D444" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A445" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B445" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C445" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D445" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A446" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B446" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C446" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D446" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A447" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B447" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C447" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D447" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A448" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B448" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C448" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D448" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A449" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B449" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C449" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D449" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A450" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B450" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C450" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D450" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A451" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B451" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C451" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D451" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A452" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B452" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C452" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D452" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A453" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B453" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C453" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D453" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A454" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C454" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D454" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A455" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B455" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C455" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D455" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A456" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B456" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C456" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D456" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A457" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C457" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D457" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A458" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C458" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D458" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A459" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C459" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D459" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A460" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C460" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D460" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A461" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C461" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D461" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A462" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C462" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D462" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A463" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B463" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C463" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D463" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A464" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C464" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D464" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A465" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C465" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D465" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A466" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C466" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D466" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A467" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C467" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D467" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A468" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C468" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D468" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A469" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C469" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D469" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A470" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C470" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D470" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A471" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C471" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D471" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A472" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C472" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D472" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A473" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C473" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D473" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A474" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C474" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D474" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A475" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C475" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D475" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A476" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C476" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D476" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A477" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C477" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D477" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A478" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C478" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D478" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A479" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C479" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D479" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A480" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C480" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D480" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A481" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C481" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D481" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A482" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C482" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D482" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A483" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C483" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D483" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A484" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C484" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D484" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A485" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C485" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D485" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A486" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B486" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C486" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D486" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A487" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B487" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C487" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D487" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A488" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C488" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D488" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A489" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C489" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D489" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A490" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C490" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D490" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A491" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C491" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D491" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A492" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C492" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D492" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A493" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B493" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C493" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D493" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A494" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C494" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D494" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A495" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C495" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D495" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A496" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C496" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D496" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A497" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C497" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D497" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A498" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C498" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D498" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A499" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C499" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D499" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A500" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D500" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A501" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C501" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D501" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A502" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C502" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D502" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A503" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C503" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D503" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A504" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C504" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D504" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A505" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C505" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D505" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A506" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C506" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D506" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A507" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C507" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D507" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A508" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C508" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D508" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A509" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D509" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A510" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D510" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A511" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D511" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A512" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C512" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D512" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A513" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C513" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D513" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A514" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C514" t="s">
+        <v>804</v>
+      </c>
+      <c r="D514" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A515" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C515" t="s">
+        <v>804</v>
+      </c>
+      <c r="D515" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A516" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C516" t="s">
+        <v>804</v>
+      </c>
+      <c r="D516" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A517" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C517" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D517" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A518" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C518" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D518" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A519" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C519" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D519" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A520" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C520" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D520" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A521" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C521" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D521" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A522" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C522" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D522" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A523" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C523" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D523" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A524" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C524" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D524" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A525" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C525" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D525" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A526" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C526" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D526" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A527" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C527" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D527" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A528" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C528" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D528" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A529" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C529" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D529" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A530" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C530" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D530" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A531" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C531" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D531" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A532" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C532" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D532" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A533" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C533" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D533" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A534" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C534" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D534" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A535" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C535" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D535" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A536" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C536" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D536" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A537" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C537" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D537" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A538" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C538" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D538" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A539" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C539" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D539" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A540" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C540" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D540" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A541" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C541" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D541" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A542" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C542" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D542" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A543" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C543" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D543" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A544" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C544" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D544" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A545" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C545" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D545" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A546" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C546" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D546" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A547" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C547" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D547" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A548" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C548" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D548" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A549" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C549" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D549" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A550" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C550" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D550" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A551" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C551" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D551" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A552" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C552" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D552" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A553" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C553" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D553" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A554" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C554" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D554" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A555" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C555" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D555" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A556" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C556" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D556" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A557" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C557" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D557" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A558" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C558" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D558" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A559" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C559" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D559" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A560" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C560" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D560" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A561" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C561" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D561" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A562" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C562" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D562" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A563" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C563" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D563" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A564" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C564" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D564" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A565" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C565" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D565" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A566" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C566" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D566" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A567" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C567" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D567" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A568" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C568" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D568" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A569" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C569" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D569" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A570" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C570" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D570" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A571" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C571" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D571" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A572" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B572" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C572" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D572" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A573" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B573" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C573" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D573" s="3" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A574" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B574" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C574" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D574" s="3" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A575" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B575" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C575" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D575" s="3" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A576" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B576" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C576" s="3" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D576" s="3" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A577" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B577" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C577" s="3" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D577" s="3" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A578" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B578" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C578" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D578" s="3" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A579" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B579" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C579" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D579" s="3" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A580" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B580" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C580" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D580" s="3" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A581" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B581" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C581" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D581" s="3" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A582" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B582" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C582" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D582" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A583" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B583" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C583" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D583" s="3" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A584" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B584" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C584" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D584" s="3" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A585" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B585" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C585" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D585" s="3" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A586" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B586" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C586" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D586" s="3" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A587" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B587" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C587" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D587" s="3" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A588" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B588" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C588" s="3" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D588" s="3" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A589" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B589" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C589" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D589" s="3" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A590" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B590" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C590" s="3" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D590" s="3" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A591" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B591" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C591" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D591" s="3" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A592" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B592" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C592" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D592" s="3" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A593" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B593" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C593" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D593" s="3" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A594" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B594" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C594" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D594" s="3" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A595" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B595" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C595" s="3" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D595" s="3" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A596" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B596" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C596" s="3" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D596" s="3" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A597" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B597" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C597" s="3" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D597" s="3" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A598" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B598" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C598" s="3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D598" s="3" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A599" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B599" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C599" s="3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D599" s="3" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A600" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B600" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C600" s="3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D600" s="3" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A601" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B601" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C601" s="3" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D601" s="3" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A602" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B602" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C602" s="3" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D602" s="3" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A603" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B603" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C603" s="3" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D603" s="3" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A604" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B604" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C604" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D604" s="3" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A605" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B605" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C605" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D605" s="3" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A606" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B606" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C606" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D606" s="3" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A607" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B607" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C607" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D607" s="3" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A608" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B608" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C608" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D608" s="3" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A609" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B609" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C609" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D609" s="3" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A610" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B610" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C610" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D610" s="3" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A611" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B611" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C611" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D611" s="3" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A612" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B612" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C612" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D612" s="3" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A613" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B613" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C613" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D613" s="3" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A614" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B614" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C614" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D614" s="3" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A615" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B615" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C615" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D615" s="3" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A616" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B616" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C616" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D616" s="3" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A617" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B617" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C617" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D617" s="3" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A618" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B618" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C618" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D618" s="3" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A619" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B619" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C619" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D619" s="3" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A620" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B620" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C620" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D620" s="3" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A621" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B621" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C621" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D621" s="3" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A622" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B622" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C622" s="3" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D622" s="3" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A623" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B623" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C623" s="3" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D623" s="3" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A624" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B624" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C624" s="3" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D624" s="3" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A625" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B625" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C625" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D625" s="3" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A626" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B626" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C626" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D626" s="3" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A627" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B627" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C627" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D627" s="3" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A628" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B628" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C628" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D628" s="3" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A629" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B629" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C629" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D629" s="3" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A630" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B630" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C630" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D630" s="3" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A631" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B631" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C631" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D631" s="3" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A632" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B632" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C632" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D632" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A633" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B633" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C633" s="3" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D633" s="3" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A634" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B634" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C634" s="3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D634" s="3" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A635" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B635" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C635" s="3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D635" s="3" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A636" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B636" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C636" s="3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D636" s="3" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A637" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B637" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C637" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D637" s="3" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A638" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B638" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C638" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D638" s="3" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A639" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B639" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C639" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D639" s="3" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A640" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B640" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C640" s="3" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D640" s="3" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A641" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B641" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C641" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D641" s="3" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A642" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B642" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C642" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D642" s="3" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A643" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B643" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C643" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D643" s="3" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A644" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B644" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C644" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D644" s="3" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A645" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B645" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C645" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D645" s="3" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A646" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B646" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C646" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D646" s="3" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A647" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B647" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C647" s="3" t="s">
+        <v>1593</v>
+      </c>
+      <c r="D647" s="3" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A648" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B648" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C648" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D648" s="3" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A649" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B649" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C649" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D649" s="3" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A650" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B650" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C650" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D650" s="3" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A651" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B651" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C651" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D651" s="3" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A652" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B652" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C652" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D652" s="3" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A653" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B653" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C653" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D653" s="3" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A654" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B654" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D654" s="3" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A655" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B655" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C655" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D655" s="3" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A656" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B656" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C656" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D656" s="3" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A657" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B657" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C657" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D657" s="3" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A658" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B658" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C658" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D658" s="3" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A659" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B659" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C659" s="3" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D659" s="3" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A660" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B660" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C660" s="3" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D660" s="3" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A661" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B661" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C661" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D661" s="3" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A662" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B662" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C662" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D662" s="3" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A663" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B663" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C663" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D663" s="3" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A664" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B664" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C664" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D664" s="3" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A665" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B665" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C665" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D665" s="3" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A666" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B666" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D666" s="3" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A667" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B667" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C667" s="3" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D667" s="3" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A668" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B668" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D668" s="3" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A669" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B669" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C669" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D669" s="3" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A670" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B670" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D670" s="3" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A671" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B671" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D671" s="3" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A672" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B672" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D672" s="3" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="673" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A673" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B673" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C673" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D673" s="3" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A674" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B674" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C674" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D674" s="3" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A675" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B675" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C675" s="3" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D675" s="3" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="676" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A676" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B676" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C676" s="3" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D676" s="3" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A677" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B677" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C677" s="3" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D677" s="3" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A678" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B678" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C678" s="3" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D678" s="3" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A679" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B679" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C679" s="3" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D679" s="3" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A680" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B680" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C680" s="3" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D680" s="3" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A681" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B681" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C681" s="3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D681" s="3" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A682" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B682" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C682" s="3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D682" s="3" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A683" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B683" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C683" s="3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D683" s="3" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A684" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B684" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C684" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D684" s="3" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A685" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B685" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C685" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D685" s="3" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A686" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B686" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C686" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D686" s="3" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A687" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B687" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C687" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D687" s="3" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A688" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B688" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C688" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D688" s="3" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A689" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B689" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C689" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D689" s="3" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A690" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B690" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C690" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D690" s="3" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A691" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B691" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C691" s="3" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D691" s="3" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A692" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B692" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C692" s="3" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D692" s="3" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A693" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B693" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C693" s="3" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D693" s="3" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A694" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B694" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C694" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D694" s="3" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A695" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B695" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C695" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D695" s="3" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A696" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B696" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C696" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D696" s="3" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A697" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B697" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C697" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D697" s="3" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A698" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B698" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C698" s="3" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D698" s="3" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A699" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B699" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C699" s="3" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D699" s="3" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A700" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B700" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C700" s="3" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D700" s="3" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A701" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B701" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C701" s="3" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D701" s="3" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A702" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B702" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C702" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D702" s="3" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A703" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B703" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C703" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D703" s="3" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A704" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B704" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C704" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D704" s="3" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A705" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B705" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C705" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D705" s="3" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A706" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B706" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C706" s="3" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D706" s="3" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A707" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B707" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C707" s="3" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D707" s="3" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A708" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B708" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C708" s="3" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D708" s="3" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A709" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B709" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C709" s="3" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D709" s="3" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A710" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B710" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C710" s="3" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D710" s="3" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A711" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B711" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C711" s="3" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D711" s="3" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A712" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B712" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C712" s="3" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D712" s="3" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A713" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B713" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C713" s="3" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D713" s="3" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A714" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B714" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C714" s="3" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D714" s="3" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A715" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B715" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C715" s="3" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D715" s="3" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A716" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B716" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C716" s="3" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D716" s="3" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A717" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B717" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C717" s="3" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D717" s="3" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A718" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B718" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C718" s="3" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D718" s="3" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="719" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A719" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B719" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C719" s="3" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D719" s="3" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="720" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A720" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B720" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C720" s="3" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D720" s="3" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="721" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A721" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B721" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C721" s="3" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D721" s="3" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="722" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A722" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B722" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C722" s="3" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D722" s="3" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="723" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A723" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B723" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C723" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D723" s="3" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="724" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A724" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B724" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C724" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D724" s="3" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="725" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A725" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B725" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C725" s="3" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D725" s="3" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="726" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A726" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B726" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C726" s="3" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D726" s="3" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="727" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A727" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B727" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C727" s="3" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D727" s="3" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="728" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A728" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B728" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C728" s="3" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D728" s="3" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="729" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A729" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B729" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C729" s="3" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D729" s="3" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="730" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A730" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B730" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C730" s="3" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D730" s="3" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="731" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A731" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B731" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C731" s="3" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D731" s="3" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="732" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A732" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B732" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C732" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D732" s="3" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="733" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A733" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B733" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C733" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D733" s="3" t="s">
+        <v>1800</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
